--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.64" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.64" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.64.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.64.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0064.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0064.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.64" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.64" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -606,11 +606,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: E.F. â€¢ &gt;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: r</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: P</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -630,7 +634,7 @@
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: E.F. â€¢ &gt;</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | abbreviation/spacing may be garbled :: E.F. • &gt;</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 1st Decemberâ€™</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | abbreviation/spacing may be garbled :: E.F. • &gt;</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L56: symbol-only separator/garbage line :: 1850.</t>
+          <t>L49: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       <c r="V3" s="1" t="inlineStr"/>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L95: abbreviation/spacing may be garbled :: A.B.in theÂ§</t>
+          <t>L95: abbreviation/spacing may be garbled :: A.B.in the§</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -716,7 +720,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Letter,â€”,</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE | isolated marker/symbol line :: ■</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -728,7 +732,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 1849.</t>
+          <t>L56: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -759,7 +763,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -779,7 +783,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 5</t>
+          <t>L59: symbol-only separator/garbage line :: 1849.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -826,7 +830,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L103: symbol-only separator/garbage line :: 1850.</t>
+          <t>L63: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -873,7 +877,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: â–</t>
+          <t>L103: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -920,7 +924,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 1850.</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE | isolated marker/symbol line :: ■</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -967,7 +971,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: R.</t>
+          <t>L124: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L130: symbol-only separator/garbage line :: 1800.</t>
+          <t>L126: isolated marker/symbol line :: R.</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1041,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1059,7 +1063,11 @@
           <t>L93: isolated marker/symbol line :: a</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr"/>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>L130: symbol-only separator/garbage line :: 1800.</t>
+        </is>
+      </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1084,7 +1092,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
